--- a/data/气动汇总表.xlsx
+++ b/data/气动汇总表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AEROlab\Project\Kirov\仿真\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06309A4C-3AA9-40DE-BFB4-3FB0DB19DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F839F81-60A2-40FF-8ED0-09705BD864D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2805" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{CDBE83F1-B213-42EE-8299-F5466D99B751}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{CDBE83F1-B213-42EE-8299-F5466D99B751}"/>
   </bookViews>
   <sheets>
     <sheet name="基本气动_体轴系" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
   <si>
     <t>ΔFx (N)</t>
   </si>
@@ -209,6 +209,10 @@
     <t>b</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>SPOILERS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -217,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +236,10 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,10 +259,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -272,7 +281,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{2098A611-A785-4968-A76E-DB0E1653D7E8}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3458,13 +3468,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A742D110-BFB9-490D-92B7-F8A631CC3792}">
   <dimension ref="A1:T84"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="10.59765625" customWidth="1"/>
-    <col min="14" max="14" width="9.06640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -3517,7 +3527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -3577,7 +3587,7 @@
         <v>-23.991339998504479</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20">
       <c r="A3" s="5"/>
       <c r="B3">
         <v>-4</v>
@@ -3635,7 +3645,7 @@
         <v>-14.99814863386089</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20">
       <c r="A4" s="5"/>
       <c r="B4">
         <v>-2</v>
@@ -3693,7 +3703,7 @@
         <v>-15.30279647963113</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:20">
       <c r="A5" s="5"/>
       <c r="B5">
         <v>0</v>
@@ -3751,7 +3761,7 @@
         <v>-12.44528079261349</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:20">
       <c r="A6" s="5"/>
       <c r="B6">
         <v>2</v>
@@ -3809,7 +3819,7 @@
         <v>-5.4940833620700849</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:20">
       <c r="A7" s="5"/>
       <c r="B7">
         <v>4</v>
@@ -3867,7 +3877,7 @@
         <v>5.7552017662756283</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:20">
       <c r="A8" s="5"/>
       <c r="B8">
         <v>6</v>
@@ -3925,7 +3935,7 @@
         <v>18.56613887146473</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:20">
       <c r="A9" s="5"/>
       <c r="B9">
         <v>8</v>
@@ -3983,7 +3993,7 @@
         <v>34.362007275630788</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10">
         <v>10</v>
@@ -4041,7 +4051,7 @@
         <v>50.862834361622447</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11">
         <v>11</v>
@@ -4099,7 +4109,7 @@
         <v>61.851394123817357</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12">
         <v>12</v>
@@ -4157,7 +4167,7 @@
         <v>69.705695340976661</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:20">
       <c r="A13" s="5"/>
       <c r="B13">
         <v>13</v>
@@ -4215,7 +4225,7 @@
         <v>75.234446847148561</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14">
         <v>14</v>
@@ -4273,7 +4283,7 @@
         <v>80.827969565604761</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20">
       <c r="A15" s="4"/>
       <c r="N15">
         <f t="shared" si="0"/>
@@ -4304,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:20">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -4364,7 +4374,7 @@
         <v>-74.009603092409151</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:20">
       <c r="A17" s="5"/>
       <c r="B17">
         <v>-4</v>
@@ -4422,7 +4432,7 @@
         <v>-74.744663242413566</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18">
         <v>-2</v>
@@ -4480,7 +4490,7 @@
         <v>-74.805886156120536</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:20">
       <c r="A19" s="5"/>
       <c r="B19">
         <v>0</v>
@@ -4538,7 +4548,7 @@
         <v>-75.473195134258248</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20">
         <v>2</v>
@@ -4596,7 +4606,7 @@
         <v>-76.399198626283521</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:20">
       <c r="A21" s="5"/>
       <c r="B21">
         <v>4</v>
@@ -4654,7 +4664,7 @@
         <v>-76.390506569264886</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22">
         <v>6</v>
@@ -4712,7 +4722,7 @@
         <v>-78.208328352224044</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23">
         <v>8</v>
@@ -4770,7 +4780,7 @@
         <v>-79.088934121897523</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:20">
       <c r="A24" s="5"/>
       <c r="B24">
         <v>10</v>
@@ -4828,7 +4838,7 @@
         <v>-75.745255179489874</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25">
         <v>11</v>
@@ -4886,7 +4896,7 @@
         <v>-73.773693566653208</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26">
         <v>12</v>
@@ -4944,7 +4954,7 @@
         <v>-72.388524946326015</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:20">
       <c r="A27" s="5"/>
       <c r="B27">
         <v>13</v>
@@ -5002,7 +5012,7 @@
         <v>-73.748145333375433</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:20">
       <c r="A28" s="5"/>
       <c r="B28">
         <v>14</v>
@@ -5060,7 +5070,7 @@
         <v>-73.82600571310914</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:20">
       <c r="A29" s="4"/>
       <c r="N29">
         <f t="shared" si="0"/>
@@ -5091,7 +5101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:20">
       <c r="A30" s="5" t="s">
         <v>17</v>
       </c>
@@ -5151,7 +5161,7 @@
         <v>44.672399281276682</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:20">
       <c r="A31" s="5"/>
       <c r="B31">
         <v>-4</v>
@@ -5209,7 +5219,7 @@
         <v>-25.584479260010081</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:20">
       <c r="A32" s="5"/>
       <c r="B32">
         <v>-2</v>
@@ -5267,7 +5277,7 @@
         <v>-106.9874629780131</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33">
         <v>0</v>
@@ -5325,7 +5335,7 @@
         <v>-185.392636714801</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:20">
       <c r="A34" s="5"/>
       <c r="B34">
         <v>2</v>
@@ -5383,7 +5393,7 @@
         <v>-261.29205769298659</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:20">
       <c r="A35" s="5"/>
       <c r="B35">
         <v>4</v>
@@ -5441,7 +5451,7 @@
         <v>-325.61234224119698</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36">
         <v>6</v>
@@ -5499,7 +5509,7 @@
         <v>-370.21927993410941</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37">
         <v>8</v>
@@ -5557,7 +5567,7 @@
         <v>-428.50735362479492</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38">
         <v>10</v>
@@ -5615,7 +5625,7 @@
         <v>-498.48252260304298</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:20">
       <c r="A39" s="5"/>
       <c r="B39">
         <v>11</v>
@@ -5673,7 +5683,7 @@
         <v>-550.97142403194823</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40">
         <v>12</v>
@@ -5731,7 +5741,7 @@
         <v>-573.60315293890881</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:20">
       <c r="A41" s="5"/>
       <c r="B41">
         <v>13</v>
@@ -5789,7 +5799,7 @@
         <v>-587.14594002348781</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:20">
       <c r="A42" s="5"/>
       <c r="B42">
         <v>14</v>
@@ -5847,7 +5857,7 @@
         <v>-597.09623405322418</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:20">
       <c r="A43" s="4"/>
       <c r="N43">
         <f t="shared" si="7"/>
@@ -5878,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:20">
       <c r="A44" s="5" t="s">
         <v>18</v>
       </c>
@@ -5938,7 +5948,7 @@
         <v>-12.658067601273803</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:20">
       <c r="A45" s="5"/>
       <c r="B45">
         <v>-4</v>
@@ -5996,7 +6006,7 @@
         <v>-25.710618730685322</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:20">
       <c r="A46" s="5"/>
       <c r="B46">
         <v>-2</v>
@@ -6054,7 +6064,7 @@
         <v>-23.743878646528678</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47">
         <v>0</v>
@@ -6112,7 +6122,7 @@
         <v>-23.332302184165385</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48">
         <v>2</v>
@@ -6170,7 +6180,7 @@
         <v>-23.773613573905109</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:20">
       <c r="A49" s="5"/>
       <c r="B49">
         <v>4</v>
@@ -6228,7 +6238,7 @@
         <v>-25.089318351861348</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:20">
       <c r="A50" s="5"/>
       <c r="B50">
         <v>6</v>
@@ -6286,7 +6296,7 @@
         <v>-30.337815188066617</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51">
         <v>8</v>
@@ -6344,7 +6354,7 @@
         <v>-33.423306293940279</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52">
         <v>10</v>
@@ -6402,7 +6412,7 @@
         <v>-32.323078699771955</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:20">
       <c r="A53" s="5"/>
       <c r="B53">
         <v>11</v>
@@ -6460,7 +6470,7 @@
         <v>-30.855273920186974</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54">
         <v>12</v>
@@ -6518,7 +6528,7 @@
         <v>-35.83488211900297</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55">
         <v>13</v>
@@ -6576,7 +6586,7 @@
         <v>-22.806765481161289</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56">
         <v>14</v>
@@ -6634,7 +6644,7 @@
         <v>-29.577264418758755</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:20">
       <c r="A57" s="4"/>
       <c r="N57">
         <f t="shared" si="7"/>
@@ -6665,7 +6675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:20">
       <c r="A58" s="5" t="s">
         <v>19</v>
       </c>
@@ -6725,7 +6735,7 @@
         <v>4.3578186284768563</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59">
         <v>-4</v>
@@ -6783,7 +6793,7 @@
         <v>-19.48596484010103</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60">
         <v>-2</v>
@@ -6841,7 +6851,7 @@
         <v>-34.740015335633871</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:20">
       <c r="A61" s="5"/>
       <c r="B61">
         <v>0</v>
@@ -6899,7 +6909,7 @@
         <v>-50.069384268656293</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:20">
       <c r="A62" s="5"/>
       <c r="B62">
         <v>2</v>
@@ -6957,7 +6967,7 @@
         <v>-63.244791656083223</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:20">
       <c r="A63" s="5"/>
       <c r="B63">
         <v>4</v>
@@ -7015,7 +7025,7 @@
         <v>-68.687453135523626</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:20">
       <c r="A64" s="5"/>
       <c r="B64">
         <v>6</v>
@@ -7073,7 +7083,7 @@
         <v>-65.163267828942907</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:20">
       <c r="A65" s="5"/>
       <c r="B65">
         <v>8</v>
@@ -7131,7 +7141,7 @@
         <v>-80.825030143681929</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:20">
       <c r="A66" s="5"/>
       <c r="B66">
         <v>10</v>
@@ -7189,7 +7199,7 @@
         <v>-113.667231478652</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:20">
       <c r="A67" s="5"/>
       <c r="B67">
         <v>11</v>
@@ -7247,7 +7257,7 @@
         <v>-142.97787536531621</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:20">
       <c r="A68" s="5"/>
       <c r="B68">
         <v>12</v>
@@ -7305,7 +7315,7 @@
         <v>-151.4869605546422</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:20">
       <c r="A69" s="5"/>
       <c r="B69">
         <v>13</v>
@@ -7363,7 +7373,7 @@
         <v>-158.6811069016218</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:20">
       <c r="A70" s="5"/>
       <c r="B70">
         <v>14</v>
@@ -7421,7 +7431,7 @@
         <v>-152.89011386670811</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:20">
       <c r="A71" s="4"/>
       <c r="N71">
         <f t="shared" si="14"/>
@@ -7452,7 +7462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:20">
       <c r="A72" s="5" t="s">
         <v>20</v>
       </c>
@@ -7512,7 +7522,7 @@
         <v>30.85497821370744</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:20">
       <c r="A73" s="5"/>
       <c r="B73">
         <v>-4</v>
@@ -7570,7 +7580,7 @@
         <v>29.614506949907337</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:20">
       <c r="A74" s="5"/>
       <c r="B74">
         <v>-2</v>
@@ -7628,7 +7638,7 @@
         <v>30.240286102669316</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:20">
       <c r="A75" s="5"/>
       <c r="B75">
         <v>0</v>
@@ -7686,7 +7696,7 @@
         <v>32.09864912168662</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:20">
       <c r="A76" s="5"/>
       <c r="B76">
         <v>2</v>
@@ -7744,7 +7754,7 @@
         <v>35.15300948549406</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:20">
       <c r="A77" s="5"/>
       <c r="B77">
         <v>4</v>
@@ -7802,7 +7812,7 @@
         <v>35.322741017058682</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:20">
       <c r="A78" s="5"/>
       <c r="B78">
         <v>6</v>
@@ -7860,7 +7870,7 @@
         <v>38.503286407167906</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:20">
       <c r="A79" s="5"/>
       <c r="B79">
         <v>8</v>
@@ -7918,7 +7928,7 @@
         <v>40.831746954233324</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:20">
       <c r="A80" s="5"/>
       <c r="B80">
         <v>10</v>
@@ -7976,7 +7986,7 @@
         <v>38.612833488572811</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:20">
       <c r="A81" s="5"/>
       <c r="B81">
         <v>11</v>
@@ -8034,7 +8044,7 @@
         <v>38.781954983431845</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:20">
       <c r="A82" s="5"/>
       <c r="B82">
         <v>12</v>
@@ -8092,7 +8102,7 @@
         <v>36.834210049286277</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:20">
       <c r="A83" s="5"/>
       <c r="B83">
         <v>13</v>
@@ -8150,7 +8160,7 @@
         <v>45.286286885484543</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:20">
       <c r="A84" s="5"/>
       <c r="B84">
         <v>14</v>
@@ -8225,13 +8235,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005272B3-68E4-4311-B6FE-16E821B34AB8}">
   <dimension ref="A1:Z84"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.796875" customWidth="1"/>
-    <col min="2" max="2" width="10.59765625" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -8281,7 +8291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -8338,7 +8348,7 @@
         <v>-23.991339998504479</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18">
       <c r="A3" s="5"/>
       <c r="B3">
         <v>-4</v>
@@ -8393,7 +8403,7 @@
         <v>-14.99814863386089</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18">
       <c r="A4" s="5"/>
       <c r="B4">
         <v>-2</v>
@@ -8448,7 +8458,7 @@
         <v>-15.30279647963113</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18">
       <c r="A5" s="5"/>
       <c r="B5">
         <v>0</v>
@@ -8503,7 +8513,7 @@
         <v>-12.44528079261349</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18">
       <c r="A6" s="5"/>
       <c r="B6">
         <v>2</v>
@@ -8558,7 +8568,7 @@
         <v>-5.4940833620700849</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18">
       <c r="A7" s="5"/>
       <c r="B7">
         <v>4</v>
@@ -8613,7 +8623,7 @@
         <v>5.7552017662756283</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18">
       <c r="A8" s="5"/>
       <c r="B8">
         <v>6</v>
@@ -8668,7 +8678,7 @@
         <v>18.56613887146473</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18">
       <c r="A9" s="5"/>
       <c r="B9">
         <v>8</v>
@@ -8723,7 +8733,7 @@
         <v>34.362007275630788</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18">
       <c r="A10" s="5"/>
       <c r="B10">
         <v>10</v>
@@ -8778,7 +8788,7 @@
         <v>50.862834361622447</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18">
       <c r="A11" s="5"/>
       <c r="B11">
         <v>11</v>
@@ -8833,7 +8843,7 @@
         <v>61.851394123817357</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18">
       <c r="A12" s="5"/>
       <c r="B12">
         <v>12</v>
@@ -8888,7 +8898,7 @@
         <v>69.705695340976661</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18">
       <c r="A13" s="5"/>
       <c r="B13">
         <v>13</v>
@@ -8943,7 +8953,7 @@
         <v>75.234446847148561</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18">
       <c r="A14" s="5"/>
       <c r="B14">
         <v>14</v>
@@ -8998,10 +9008,10 @@
         <v>80.827969565604761</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18">
       <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
@@ -9058,7 +9068,7 @@
         <v>-74.009603092409151</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:18">
       <c r="A17" s="5"/>
       <c r="B17">
         <v>-4</v>
@@ -9113,7 +9123,7 @@
         <v>-74.744663242413566</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:18">
       <c r="A18" s="5"/>
       <c r="B18">
         <v>-2</v>
@@ -9168,7 +9178,7 @@
         <v>-74.805886156120536</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:18">
       <c r="A19" s="5"/>
       <c r="B19">
         <v>0</v>
@@ -9223,7 +9233,7 @@
         <v>-75.473195134258248</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:18">
       <c r="A20" s="5"/>
       <c r="B20">
         <v>2</v>
@@ -9278,7 +9288,7 @@
         <v>-76.399198626283521</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:18">
       <c r="A21" s="5"/>
       <c r="B21">
         <v>4</v>
@@ -9333,7 +9343,7 @@
         <v>-76.390506569264886</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:18">
       <c r="A22" s="5"/>
       <c r="B22">
         <v>6</v>
@@ -9388,7 +9398,7 @@
         <v>-78.208328352224044</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:18">
       <c r="A23" s="5"/>
       <c r="B23">
         <v>8</v>
@@ -9443,7 +9453,7 @@
         <v>-79.088934121897523</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:18">
       <c r="A24" s="5"/>
       <c r="B24">
         <v>10</v>
@@ -9498,7 +9508,7 @@
         <v>-75.745255179489874</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:18">
       <c r="A25" s="5"/>
       <c r="B25">
         <v>11</v>
@@ -9553,7 +9563,7 @@
         <v>-73.773693566653208</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:18">
       <c r="A26" s="5"/>
       <c r="B26">
         <v>12</v>
@@ -9608,7 +9618,7 @@
         <v>-72.388524946326015</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:18">
       <c r="A27" s="5"/>
       <c r="B27">
         <v>13</v>
@@ -9663,7 +9673,7 @@
         <v>-73.748145333375433</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:18">
       <c r="A28" s="5"/>
       <c r="B28">
         <v>14</v>
@@ -9718,10 +9728,10 @@
         <v>-73.82600571310914</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:18">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:18">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -9778,7 +9788,7 @@
         <v>44.672399281276682</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:18">
       <c r="A31" s="5"/>
       <c r="B31">
         <v>-4</v>
@@ -9833,7 +9843,7 @@
         <v>-25.584479260010081</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:18">
       <c r="A32" s="5"/>
       <c r="B32">
         <v>-2</v>
@@ -9888,7 +9898,7 @@
         <v>-106.9874629780131</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:26">
       <c r="A33" s="5"/>
       <c r="B33">
         <v>0</v>
@@ -9943,7 +9953,7 @@
         <v>-185.392636714801</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:26">
       <c r="A34" s="5"/>
       <c r="B34">
         <v>2</v>
@@ -9998,7 +10008,7 @@
         <v>-261.29205769298659</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:26">
       <c r="A35" s="5"/>
       <c r="B35">
         <v>4</v>
@@ -10053,7 +10063,7 @@
         <v>-325.61234224119698</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:26">
       <c r="A36" s="5"/>
       <c r="B36">
         <v>6</v>
@@ -10108,7 +10118,7 @@
         <v>-370.21927993410941</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:26">
       <c r="A37" s="5"/>
       <c r="B37">
         <v>8</v>
@@ -10163,7 +10173,7 @@
         <v>-428.50735362479492</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:26">
       <c r="A38" s="5"/>
       <c r="B38">
         <v>10</v>
@@ -10218,7 +10228,7 @@
         <v>-498.48252260304298</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:26">
       <c r="A39" s="5"/>
       <c r="B39">
         <v>11</v>
@@ -10273,7 +10283,7 @@
         <v>-550.97142403194823</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:26">
       <c r="A40" s="5"/>
       <c r="B40">
         <v>12</v>
@@ -10328,7 +10338,7 @@
         <v>-573.60315293890881</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:26">
       <c r="A41" s="5"/>
       <c r="B41">
         <v>13</v>
@@ -10383,7 +10393,7 @@
         <v>-587.14594002348781</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:26">
       <c r="A42" s="5"/>
       <c r="B42">
         <v>14</v>
@@ -10438,10 +10448,10 @@
         <v>-597.09623405322418</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:26">
       <c r="A43" s="4"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:26">
       <c r="A44" s="5" t="s">
         <v>28</v>
       </c>
@@ -10526,7 +10536,7 @@
         <v>-12.658067601273803</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:26">
       <c r="A45" s="5"/>
       <c r="B45">
         <v>-4</v>
@@ -10609,7 +10619,7 @@
         <v>-25.710618730685322</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:26">
       <c r="A46" s="5"/>
       <c r="B46">
         <v>-2</v>
@@ -10692,7 +10702,7 @@
         <v>-23.743878646528678</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:26">
       <c r="A47" s="5"/>
       <c r="B47">
         <v>0</v>
@@ -10775,7 +10785,7 @@
         <v>-23.332302184165385</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:26">
       <c r="A48" s="5"/>
       <c r="B48">
         <v>2</v>
@@ -10858,7 +10868,7 @@
         <v>-23.773613573905109</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26">
       <c r="A49" s="5"/>
       <c r="B49">
         <v>4</v>
@@ -10941,7 +10951,7 @@
         <v>-25.089318351861348</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:26">
       <c r="A50" s="5"/>
       <c r="B50">
         <v>6</v>
@@ -11024,7 +11034,7 @@
         <v>-30.337815188066617</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26">
       <c r="A51" s="5"/>
       <c r="B51">
         <v>8</v>
@@ -11107,7 +11117,7 @@
         <v>-33.423306293940279</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26">
       <c r="A52" s="5"/>
       <c r="B52">
         <v>10</v>
@@ -11190,7 +11200,7 @@
         <v>-32.323078699771955</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:26">
       <c r="A53" s="5"/>
       <c r="B53">
         <v>11</v>
@@ -11273,7 +11283,7 @@
         <v>-30.855273920186974</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:26">
       <c r="A54" s="5"/>
       <c r="B54">
         <v>12</v>
@@ -11356,7 +11366,7 @@
         <v>-35.83488211900297</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:26">
       <c r="A55" s="5"/>
       <c r="B55">
         <v>13</v>
@@ -11439,7 +11449,7 @@
         <v>-22.806765481161289</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:26">
       <c r="A56" s="5"/>
       <c r="B56">
         <v>14</v>
@@ -11522,10 +11532,10 @@
         <v>-29.577264418758755</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:26">
       <c r="A57" s="4"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:26">
       <c r="A58" s="5" t="s">
         <v>29</v>
       </c>
@@ -11610,7 +11620,7 @@
         <v>-3.10247205149635</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:26">
       <c r="A59" s="5"/>
       <c r="B59">
         <v>-4</v>
@@ -11693,7 +11703,7 @@
         <v>-15.213356803679346</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:26">
       <c r="A60" s="5"/>
       <c r="B60">
         <v>-2</v>
@@ -11776,7 +11786,7 @@
         <v>-16.873109018305684</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:26">
       <c r="A61" s="5"/>
       <c r="B61">
         <v>0</v>
@@ -11859,7 +11869,7 @@
         <v>-19.108813937284523</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:26">
       <c r="A62" s="5"/>
       <c r="B62">
         <v>2</v>
@@ -11942,7 +11952,7 @@
         <v>-19.609018021354458</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:26">
       <c r="A63" s="5"/>
       <c r="B63">
         <v>4</v>
@@ -12025,7 +12035,7 @@
         <v>-14.310191981243726</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:26">
       <c r="A64" s="5"/>
       <c r="B64">
         <v>6</v>
@@ -12108,7 +12118,7 @@
         <v>-3.3366480799466345</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:26">
       <c r="A65" s="5"/>
       <c r="B65">
         <v>8</v>
@@ -12191,7 +12201,7 @@
         <v>-9.264302088341168</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:26">
       <c r="A66" s="5"/>
       <c r="B66">
         <v>10</v>
@@ -12274,7 +12284,7 @@
         <v>-30.420650203943822</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:26">
       <c r="A67" s="5"/>
       <c r="B67">
         <v>11</v>
@@ -12357,7 +12367,7 @@
         <v>-50.965647551980851</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:26">
       <c r="A68" s="5"/>
       <c r="B68">
         <v>12</v>
@@ -12440,7 +12450,7 @@
         <v>-55.695234013844413</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:26">
       <c r="A69" s="5"/>
       <c r="B69">
         <v>13</v>
@@ -12523,7 +12533,7 @@
         <v>-60.627734917699328</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:26">
       <c r="A70" s="5"/>
       <c r="B70">
         <v>14</v>
@@ -12606,10 +12616,10 @@
         <v>-53.175042779819663</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:26">
       <c r="A71" s="4"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:26">
       <c r="A72" s="5" t="s">
         <v>30</v>
       </c>
@@ -12694,7 +12704,7 @@
         <v>18.495374497275112</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:26">
       <c r="A73" s="5"/>
       <c r="B73">
         <v>-4</v>
@@ -12777,7 +12787,7 @@
         <v>17.132148188424271</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:26">
       <c r="A74" s="5"/>
       <c r="B74">
         <v>-2</v>
@@ -12860,7 +12870,7 @@
         <v>17.747703114597186</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:26">
       <c r="A75" s="5"/>
       <c r="B75">
         <v>0</v>
@@ -12943,7 +12953,7 @@
         <v>19.494625534265491</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:26">
       <c r="A76" s="5"/>
       <c r="B76">
         <v>2</v>
@@ -13026,7 +13036,7 @@
         <v>22.39434331490471</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:26">
       <c r="A77" s="5"/>
       <c r="B77">
         <v>4</v>
@@ -13109,7 +13119,7 @@
         <v>22.565526419991446</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:26">
       <c r="A78" s="5"/>
       <c r="B78">
         <v>6</v>
@@ -13192,7 +13202,7 @@
         <v>25.442495572346488</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:26">
       <c r="A79" s="5"/>
       <c r="B79">
         <v>8</v>
@@ -13275,7 +13285,7 @@
         <v>27.623894955876438</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:26">
       <c r="A80" s="5"/>
       <c r="B80">
         <v>10</v>
@@ -13358,7 +13368,7 @@
         <v>25.963375873598004</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:26">
       <c r="A81" s="5"/>
       <c r="B81">
         <v>11</v>
@@ -13441,7 +13451,7 @@
         <v>26.461748157800759</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:26">
       <c r="A82" s="5"/>
       <c r="B82">
         <v>12</v>
@@ -13524,7 +13534,7 @@
         <v>24.745326383249832</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:26">
       <c r="A83" s="5"/>
       <c r="B83">
         <v>13</v>
@@ -13607,7 +13617,7 @@
         <v>32.970346614810843</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:26">
       <c r="A84" s="5"/>
       <c r="B84">
         <v>14</v>
@@ -13706,19 +13716,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6172478-EC75-43C1-9FB0-A15B71A2EF1B}">
-  <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="10.53125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" customWidth="1"/>
-    <col min="5" max="5" width="11.46484375" customWidth="1"/>
-    <col min="6" max="6" width="12.06640625" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" customWidth="1"/>
-    <col min="8" max="8" width="14.796875" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -13744,7 +13754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>-30</v>
       </c>
@@ -13767,7 +13777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>-20</v>
       </c>
@@ -13790,7 +13800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>-10</v>
       </c>
@@ -13813,7 +13823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -13836,7 +13846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>10</v>
       </c>
@@ -13859,7 +13869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>20</v>
       </c>
@@ -13882,7 +13892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>30</v>
       </c>
@@ -13905,7 +13915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -13931,7 +13941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>-30</v>
       </c>
@@ -13954,7 +13964,7 @@
         <v>-12.38351762326886</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>-20</v>
       </c>
@@ -13977,7 +13987,7 @@
         <v>-7.7971080259004211</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>-10</v>
       </c>
@@ -14000,7 +14010,7 @@
         <v>-2.8220299560880799</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -14023,7 +14033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -14046,7 +14056,7 @@
         <v>-0.70988111902298856</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>20</v>
       </c>
@@ -14069,7 +14079,7 @@
         <v>-4.9267742162711183</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>30</v>
       </c>
@@ -14092,7 +14102,7 @@
         <v>-11.495385151368909</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -14118,7 +14128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>-30</v>
       </c>
@@ -14147,7 +14157,7 @@
         <v>11.495385151368909</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>-20</v>
       </c>
@@ -14176,7 +14186,7 @@
         <v>4.9267742162711183</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>-10</v>
       </c>
@@ -14205,7 +14215,7 @@
         <v>0.70988111902298856</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -14228,7 +14238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>10</v>
       </c>
@@ -14257,7 +14267,7 @@
         <v>2.8220299560880799</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>20</v>
       </c>
@@ -14286,7 +14296,7 @@
         <v>7.7971080259004211</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>30</v>
       </c>
@@ -14315,7 +14325,7 @@
         <v>12.38351762326886</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -14341,7 +14351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>-30</v>
       </c>
@@ -14370,7 +14380,7 @@
         <v>127.804461821706</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>-20</v>
       </c>
@@ -14399,7 +14409,7 @@
         <v>106.8043006598031</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>-10</v>
       </c>
@@ -14428,7 +14438,7 @@
         <v>70.957642628593192</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8">
       <c r="A32" s="2">
         <v>0</v>
       </c>
@@ -14451,7 +14461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7">
       <c r="A33" s="2">
         <v>10</v>
       </c>
@@ -14474,7 +14484,7 @@
         <v>-70.957642628593192</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7">
       <c r="A34" s="2">
         <v>20</v>
       </c>
@@ -14497,7 +14507,7 @@
         <v>-106.8043006598031</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7">
       <c r="A35" s="2">
         <v>30</v>
       </c>
@@ -14520,7 +14530,7 @@
         <v>-127.804461821706</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -14543,7 +14553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7">
       <c r="A38" s="2">
         <v>0</v>
       </c>
@@ -14566,7 +14576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7">
       <c r="A39" s="2">
         <v>1</v>
       </c>
@@ -14589,7 +14599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7">
       <c r="A40" s="2">
         <v>2</v>
       </c>
@@ -14609,6 +14619,190 @@
         <v>-47.705650139624908</v>
       </c>
       <c r="G40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>10</v>
+      </c>
+      <c r="B44">
+        <v>-6.0028055283282811E-2</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>184.69285693131889</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>30.688250375420672</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
+        <v>20</v>
+      </c>
+      <c r="B45">
+        <v>-5.1244774716067738</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>265.91955851333262</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>42.975884017481718</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
+        <v>30</v>
+      </c>
+      <c r="B46">
+        <v>-12.148573818769364</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>336.39869540463008</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>53.623398644051207</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
+        <v>40</v>
+      </c>
+      <c r="B47">
+        <v>-20.595611451758778</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>392.03499021397556</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>62.162433065266328</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
+        <v>50</v>
+      </c>
+      <c r="B48">
+        <v>-27.581248876293316</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>422.82479974122174</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>66.657778284712208</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
+        <v>60</v>
+      </c>
+      <c r="B49">
+        <v>-33.062854183439967</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>442.95088942859672</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>69.208923117121998</v>
+      </c>
+      <c r="G49" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14625,9 +14819,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB2D269-1CEB-4E31-875B-88666882F966}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -14635,7 +14829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -14643,7 +14837,7 @@
         <v>-45.848999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -14651,7 +14845,7 @@
         <v>-3.0775999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -14659,7 +14853,7 @@
         <v>13.004</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -14667,7 +14861,7 @@
         <v>5.8177000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -14675,7 +14869,7 @@
         <v>-0.62892999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -14683,7 +14877,7 @@
         <v>0.15584999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -14691,7 +14885,7 @@
         <v>-0.11662</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -14699,7 +14893,7 @@
         <v>2.0151000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -14707,7 +14901,7 @@
         <v>-0.36527999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -14715,7 +14909,7 @@
         <v>0.36157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -14723,7 +14917,7 @@
         <v>2.4550000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -14731,7 +14925,7 @@
         <v>0.42899999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>45</v>
       </c>

--- a/data/气动汇总表.xlsx
+++ b/data/气动汇总表.xlsx
@@ -2,27 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AEROlab\Project\Kirov\仿真\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F839F81-60A2-40FF-8ED0-09705BD864D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAA132E-C794-4C93-845A-C6F2FD96E04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{CDBE83F1-B213-42EE-8299-F5466D99B751}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基本气动_体轴系" sheetId="3" r:id="rId1"/>
     <sheet name="基本气动_风轴系" sheetId="2" r:id="rId2"/>
     <sheet name="舵效" sheetId="1" r:id="rId3"/>
     <sheet name="动导数" sheetId="4" r:id="rId4"/>
+    <sheet name="地效" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,59 +37,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
   <si>
-    <t>ΔFx (N)</t>
-  </si>
-  <si>
-    <t>ΔFy (N)</t>
-  </si>
-  <si>
-    <t>ΔFz (N)</t>
-  </si>
-  <si>
-    <t>ΔMx (N·m)</t>
-  </si>
-  <si>
-    <t>ΔMy (N·m)</t>
-  </si>
-  <si>
-    <t>ΔMz (N·m)</t>
-  </si>
-  <si>
-    <t>ELEV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LAILE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAILE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>舵面向下为正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>舵面向上为正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FLAPS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RUDD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从后面看舵面向左为正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>ref分量</t>
   </si>
   <si>
     <t>迎角 α [deg]</t>
+  </si>
+  <si>
+    <t>基准</t>
+  </si>
+  <si>
+    <t>侧滑增量</t>
   </si>
   <si>
     <t>Fx [N]</t>
@@ -112,106 +69,139 @@
     <t>Mz_ref [N·m]</t>
   </si>
   <si>
-    <t>基准</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ref分量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侧滑增量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>wind</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>L [N]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>D [N]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Y [N]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>L_CG [N·m]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>M_CG [N·m]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>N_CG [N·m]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELEV</t>
+  </si>
+  <si>
+    <t>ΔFx (N)</t>
+  </si>
+  <si>
+    <t>ΔFy (N)</t>
+  </si>
+  <si>
+    <t>ΔFz (N)</t>
+  </si>
+  <si>
+    <t>ΔMx (N·m)</t>
+  </si>
+  <si>
+    <t>ΔMy (N·m)</t>
+  </si>
+  <si>
+    <t>ΔMz (N·m)</t>
+  </si>
+  <si>
+    <t>舵面向下为正</t>
+  </si>
+  <si>
+    <t>LAILE</t>
+  </si>
+  <si>
+    <t>舵面向上为正</t>
+  </si>
+  <si>
+    <t>RAILE</t>
+  </si>
+  <si>
+    <t>RUDD</t>
+  </si>
+  <si>
+    <t>从后面看舵面向左为正</t>
+  </si>
+  <si>
+    <t>FLAPS</t>
+  </si>
+  <si>
+    <t>SPOILERS</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>数据</t>
   </si>
   <si>
     <t>Cmq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>项目</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Cma</t>
   </si>
   <si>
     <t>CLq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CLa</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cma</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Clp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clr</t>
+  </si>
+  <si>
+    <t>Clb</t>
   </si>
   <si>
     <t>Cnp</t>
   </si>
   <si>
     <t>Cnr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Cnb</t>
   </si>
   <si>
     <t>S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SPOILERS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>kInduced</t>
+  </si>
+  <si>
+    <t>minWingHeight</t>
+  </si>
+  <si>
+    <t>alphaFull</t>
+  </si>
+  <si>
+    <t>alphaOff</t>
+  </si>
+  <si>
+    <t>heightFadeStart</t>
+  </si>
+  <si>
+    <t>heightOff</t>
+  </si>
+  <si>
+    <t>betaFull</t>
+  </si>
+  <si>
+    <t>betaOff</t>
   </si>
 </sst>
 </file>
@@ -221,25 +211,36 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -263,9 +264,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -278,11 +279,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{2098A611-A785-4968-A76E-DB0E1653D7E8}"/>
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -315,11 +325,11 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:r>
+              <a:rPr sz="1400" b="0" i="0" u="none" spc="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -327,64 +337,31 @@
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-CN"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:rPr>
               <a:t>ELEV</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -398,7 +375,6 @@
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -461,10 +437,10 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CF4A-428B-826D-01828F3EECB8}"/>
+              <c16:uniqueId val="{00000000-92B3-487B-B1EC-303078F65C2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -480,6 +456,63 @@
         <c:axId val="557812784"/>
       </c:scatterChart>
       <c:valAx>
+        <c:axId val="557812784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1232908464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
         <c:axId val="1232908464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -488,16 +521,14 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cmpd="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -505,24 +536,21 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cmpd="sng">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="25000"/>
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -530,8 +558,8 @@
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="zh-CN"/>
@@ -541,112 +569,30 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="557812784"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1232908464"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cmpd="sng">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -672,11 +618,11 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:r>
+              <a:rPr sz="1400" b="0" i="0" u="none" spc="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -684,64 +630,31 @@
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-CN"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:rPr>
               <a:t>AILE</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -755,7 +668,6 @@
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -818,10 +730,10 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F99B-4C36-9007-D4E377C51EE8}"/>
+              <c16:uniqueId val="{00000000-91EF-4DEF-AB38-06348C883427}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -837,6 +749,63 @@
         <c:axId val="557799344"/>
       </c:scatterChart>
       <c:valAx>
+        <c:axId val="557799344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1229299040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
         <c:axId val="1229299040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -845,16 +814,14 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cmpd="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -862,24 +829,21 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cmpd="sng">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="25000"/>
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -887,8 +851,8 @@
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="zh-CN"/>
@@ -898,112 +862,30 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="557799344"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1229299040"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cmpd="sng">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1029,11 +911,11 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:r>
+              <a:rPr sz="1400" b="0" i="0" u="none" spc="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1041,64 +923,31 @@
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-CN"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:rPr>
               <a:t>RUDD</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1112,7 +961,6 @@
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -1175,10 +1023,10 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-738C-4C1B-B8A0-99368C5271C4}"/>
+              <c16:uniqueId val="{00000000-A62D-47F7-9EBE-319812504D1A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1194,6 +1042,63 @@
         <c:axId val="1198177392"/>
       </c:scatterChart>
       <c:valAx>
+        <c:axId val="1198177392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1200985536"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
         <c:axId val="1200985536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -1202,16 +1107,14 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cmpd="sng">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1219,24 +1122,21 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cmpd="sng">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="25000"/>
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1244,8 +1144,8 @@
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:ea typeface="+mn-lt"/>
+                <a:cs typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="zh-CN"/>
@@ -1255,1786 +1155,36 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="1198177392"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1200985536"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cmpd="sng">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3054,10 +1204,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1">
+        <xdr:cNvPr id="2" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65132659-A875-A079-2834-F0E770EBBE32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3090,10 +1240,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2">
+        <xdr:cNvPr id="3" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57930E24-8362-0032-CB48-16FB4FEA96AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3126,10 +1276,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="图表 3">
+        <xdr:cNvPr id="4" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91482FF-E95B-30E9-82FA-52526C43F6BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3193,108 +1343,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3306,23 +1362,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -3332,23 +1388,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -3356,26 +1412,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -3410,17 +1463,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -3435,38 +1488,13 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A742D110-BFB9-490D-92B7-F8A631CC3792}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T84"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
@@ -3476,16 +1504,16 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F1">
         <v>2</v>
@@ -3528,8 +1556,8 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
+      <c r="A2" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>-6</v>
@@ -3588,7 +1616,7 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="5"/>
+      <c r="A3" s="8"/>
       <c r="B3">
         <v>-4</v>
       </c>
@@ -3646,7 +1674,7 @@
       </c>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="5"/>
+      <c r="A4" s="8"/>
       <c r="B4">
         <v>-2</v>
       </c>
@@ -3704,7 +1732,7 @@
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="5"/>
+      <c r="A5" s="8"/>
       <c r="B5">
         <v>0</v>
       </c>
@@ -3762,7 +1790,7 @@
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="5"/>
+      <c r="A6" s="8"/>
       <c r="B6">
         <v>2</v>
       </c>
@@ -3820,7 +1848,7 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="5"/>
+      <c r="A7" s="8"/>
       <c r="B7">
         <v>4</v>
       </c>
@@ -3878,7 +1906,7 @@
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="5"/>
+      <c r="A8" s="8"/>
       <c r="B8">
         <v>6</v>
       </c>
@@ -3936,7 +1964,7 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="5"/>
+      <c r="A9" s="8"/>
       <c r="B9">
         <v>8</v>
       </c>
@@ -3994,7 +2022,7 @@
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="5"/>
+      <c r="A10" s="8"/>
       <c r="B10">
         <v>10</v>
       </c>
@@ -4052,7 +2080,7 @@
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="5"/>
+      <c r="A11" s="8"/>
       <c r="B11">
         <v>11</v>
       </c>
@@ -4110,7 +2138,7 @@
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="5"/>
+      <c r="A12" s="8"/>
       <c r="B12">
         <v>12</v>
       </c>
@@ -4168,7 +2196,7 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="5"/>
+      <c r="A13" s="8"/>
       <c r="B13">
         <v>13</v>
       </c>
@@ -4226,7 +2254,7 @@
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="5"/>
+      <c r="A14" s="8"/>
       <c r="B14">
         <v>14</v>
       </c>
@@ -4315,8 +2343,8 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="5" t="s">
-        <v>16</v>
+      <c r="A16" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="B16">
         <v>-6</v>
@@ -4375,7 +2403,7 @@
       </c>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="5"/>
+      <c r="A17" s="8"/>
       <c r="B17">
         <v>-4</v>
       </c>
@@ -4433,7 +2461,7 @@
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="5"/>
+      <c r="A18" s="8"/>
       <c r="B18">
         <v>-2</v>
       </c>
@@ -4491,7 +2519,7 @@
       </c>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="5"/>
+      <c r="A19" s="8"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -4549,7 +2577,7 @@
       </c>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="5"/>
+      <c r="A20" s="8"/>
       <c r="B20">
         <v>2</v>
       </c>
@@ -4607,7 +2635,7 @@
       </c>
     </row>
     <row r="21" spans="1:20">
-      <c r="A21" s="5"/>
+      <c r="A21" s="8"/>
       <c r="B21">
         <v>4</v>
       </c>
@@ -4665,7 +2693,7 @@
       </c>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="5"/>
+      <c r="A22" s="8"/>
       <c r="B22">
         <v>6</v>
       </c>
@@ -4723,7 +2751,7 @@
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="5"/>
+      <c r="A23" s="8"/>
       <c r="B23">
         <v>8</v>
       </c>
@@ -4781,7 +2809,7 @@
       </c>
     </row>
     <row r="24" spans="1:20">
-      <c r="A24" s="5"/>
+      <c r="A24" s="8"/>
       <c r="B24">
         <v>10</v>
       </c>
@@ -4839,7 +2867,7 @@
       </c>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="5"/>
+      <c r="A25" s="8"/>
       <c r="B25">
         <v>11</v>
       </c>
@@ -4897,7 +2925,7 @@
       </c>
     </row>
     <row r="26" spans="1:20">
-      <c r="A26" s="5"/>
+      <c r="A26" s="8"/>
       <c r="B26">
         <v>12</v>
       </c>
@@ -4955,7 +2983,7 @@
       </c>
     </row>
     <row r="27" spans="1:20">
-      <c r="A27" s="5"/>
+      <c r="A27" s="8"/>
       <c r="B27">
         <v>13</v>
       </c>
@@ -5013,7 +3041,7 @@
       </c>
     </row>
     <row r="28" spans="1:20">
-      <c r="A28" s="5"/>
+      <c r="A28" s="8"/>
       <c r="B28">
         <v>14</v>
       </c>
@@ -5102,8 +3130,8 @@
       </c>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="5" t="s">
-        <v>17</v>
+      <c r="A30" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="B30">
         <v>-6</v>
@@ -5162,7 +3190,7 @@
       </c>
     </row>
     <row r="31" spans="1:20">
-      <c r="A31" s="5"/>
+      <c r="A31" s="8"/>
       <c r="B31">
         <v>-4</v>
       </c>
@@ -5220,7 +3248,7 @@
       </c>
     </row>
     <row r="32" spans="1:20">
-      <c r="A32" s="5"/>
+      <c r="A32" s="8"/>
       <c r="B32">
         <v>-2</v>
       </c>
@@ -5278,7 +3306,7 @@
       </c>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" s="5"/>
+      <c r="A33" s="8"/>
       <c r="B33">
         <v>0</v>
       </c>
@@ -5336,7 +3364,7 @@
       </c>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" s="5"/>
+      <c r="A34" s="8"/>
       <c r="B34">
         <v>2</v>
       </c>
@@ -5394,7 +3422,7 @@
       </c>
     </row>
     <row r="35" spans="1:20">
-      <c r="A35" s="5"/>
+      <c r="A35" s="8"/>
       <c r="B35">
         <v>4</v>
       </c>
@@ -5452,7 +3480,7 @@
       </c>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="5"/>
+      <c r="A36" s="8"/>
       <c r="B36">
         <v>6</v>
       </c>
@@ -5510,7 +3538,7 @@
       </c>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" s="5"/>
+      <c r="A37" s="8"/>
       <c r="B37">
         <v>8</v>
       </c>
@@ -5568,7 +3596,7 @@
       </c>
     </row>
     <row r="38" spans="1:20">
-      <c r="A38" s="5"/>
+      <c r="A38" s="8"/>
       <c r="B38">
         <v>10</v>
       </c>
@@ -5626,7 +3654,7 @@
       </c>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="5"/>
+      <c r="A39" s="8"/>
       <c r="B39">
         <v>11</v>
       </c>
@@ -5684,7 +3712,7 @@
       </c>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" s="5"/>
+      <c r="A40" s="8"/>
       <c r="B40">
         <v>12</v>
       </c>
@@ -5742,7 +3770,7 @@
       </c>
     </row>
     <row r="41" spans="1:20">
-      <c r="A41" s="5"/>
+      <c r="A41" s="8"/>
       <c r="B41">
         <v>13</v>
       </c>
@@ -5800,7 +3828,7 @@
       </c>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" s="5"/>
+      <c r="A42" s="8"/>
       <c r="B42">
         <v>14</v>
       </c>
@@ -5889,8 +3917,8 @@
       </c>
     </row>
     <row r="44" spans="1:20">
-      <c r="A44" s="5" t="s">
-        <v>18</v>
+      <c r="A44" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="B44">
         <v>-6</v>
@@ -5949,7 +3977,7 @@
       </c>
     </row>
     <row r="45" spans="1:20">
-      <c r="A45" s="5"/>
+      <c r="A45" s="8"/>
       <c r="B45">
         <v>-4</v>
       </c>
@@ -6007,7 +4035,7 @@
       </c>
     </row>
     <row r="46" spans="1:20">
-      <c r="A46" s="5"/>
+      <c r="A46" s="8"/>
       <c r="B46">
         <v>-2</v>
       </c>
@@ -6065,7 +4093,7 @@
       </c>
     </row>
     <row r="47" spans="1:20">
-      <c r="A47" s="5"/>
+      <c r="A47" s="8"/>
       <c r="B47">
         <v>0</v>
       </c>
@@ -6123,7 +4151,7 @@
       </c>
     </row>
     <row r="48" spans="1:20">
-      <c r="A48" s="5"/>
+      <c r="A48" s="8"/>
       <c r="B48">
         <v>2</v>
       </c>
@@ -6181,7 +4209,7 @@
       </c>
     </row>
     <row r="49" spans="1:20">
-      <c r="A49" s="5"/>
+      <c r="A49" s="8"/>
       <c r="B49">
         <v>4</v>
       </c>
@@ -6239,7 +4267,7 @@
       </c>
     </row>
     <row r="50" spans="1:20">
-      <c r="A50" s="5"/>
+      <c r="A50" s="8"/>
       <c r="B50">
         <v>6</v>
       </c>
@@ -6297,7 +4325,7 @@
       </c>
     </row>
     <row r="51" spans="1:20">
-      <c r="A51" s="5"/>
+      <c r="A51" s="8"/>
       <c r="B51">
         <v>8</v>
       </c>
@@ -6355,7 +4383,7 @@
       </c>
     </row>
     <row r="52" spans="1:20">
-      <c r="A52" s="5"/>
+      <c r="A52" s="8"/>
       <c r="B52">
         <v>10</v>
       </c>
@@ -6413,7 +4441,7 @@
       </c>
     </row>
     <row r="53" spans="1:20">
-      <c r="A53" s="5"/>
+      <c r="A53" s="8"/>
       <c r="B53">
         <v>11</v>
       </c>
@@ -6471,7 +4499,7 @@
       </c>
     </row>
     <row r="54" spans="1:20">
-      <c r="A54" s="5"/>
+      <c r="A54" s="8"/>
       <c r="B54">
         <v>12</v>
       </c>
@@ -6529,7 +4557,7 @@
       </c>
     </row>
     <row r="55" spans="1:20">
-      <c r="A55" s="5"/>
+      <c r="A55" s="8"/>
       <c r="B55">
         <v>13</v>
       </c>
@@ -6587,7 +4615,7 @@
       </c>
     </row>
     <row r="56" spans="1:20">
-      <c r="A56" s="5"/>
+      <c r="A56" s="8"/>
       <c r="B56">
         <v>14</v>
       </c>
@@ -6676,8 +4704,8 @@
       </c>
     </row>
     <row r="58" spans="1:20">
-      <c r="A58" s="5" t="s">
-        <v>19</v>
+      <c r="A58" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="B58">
         <v>-6</v>
@@ -6736,7 +4764,7 @@
       </c>
     </row>
     <row r="59" spans="1:20">
-      <c r="A59" s="5"/>
+      <c r="A59" s="8"/>
       <c r="B59">
         <v>-4</v>
       </c>
@@ -6794,7 +4822,7 @@
       </c>
     </row>
     <row r="60" spans="1:20">
-      <c r="A60" s="5"/>
+      <c r="A60" s="8"/>
       <c r="B60">
         <v>-2</v>
       </c>
@@ -6852,7 +4880,7 @@
       </c>
     </row>
     <row r="61" spans="1:20">
-      <c r="A61" s="5"/>
+      <c r="A61" s="8"/>
       <c r="B61">
         <v>0</v>
       </c>
@@ -6910,7 +4938,7 @@
       </c>
     </row>
     <row r="62" spans="1:20">
-      <c r="A62" s="5"/>
+      <c r="A62" s="8"/>
       <c r="B62">
         <v>2</v>
       </c>
@@ -6968,7 +4996,7 @@
       </c>
     </row>
     <row r="63" spans="1:20">
-      <c r="A63" s="5"/>
+      <c r="A63" s="8"/>
       <c r="B63">
         <v>4</v>
       </c>
@@ -7026,7 +5054,7 @@
       </c>
     </row>
     <row r="64" spans="1:20">
-      <c r="A64" s="5"/>
+      <c r="A64" s="8"/>
       <c r="B64">
         <v>6</v>
       </c>
@@ -7084,7 +5112,7 @@
       </c>
     </row>
     <row r="65" spans="1:20">
-      <c r="A65" s="5"/>
+      <c r="A65" s="8"/>
       <c r="B65">
         <v>8</v>
       </c>
@@ -7142,7 +5170,7 @@
       </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="5"/>
+      <c r="A66" s="8"/>
       <c r="B66">
         <v>10</v>
       </c>
@@ -7200,7 +5228,7 @@
       </c>
     </row>
     <row r="67" spans="1:20">
-      <c r="A67" s="5"/>
+      <c r="A67" s="8"/>
       <c r="B67">
         <v>11</v>
       </c>
@@ -7258,7 +5286,7 @@
       </c>
     </row>
     <row r="68" spans="1:20">
-      <c r="A68" s="5"/>
+      <c r="A68" s="8"/>
       <c r="B68">
         <v>12</v>
       </c>
@@ -7316,7 +5344,7 @@
       </c>
     </row>
     <row r="69" spans="1:20">
-      <c r="A69" s="5"/>
+      <c r="A69" s="8"/>
       <c r="B69">
         <v>13</v>
       </c>
@@ -7374,7 +5402,7 @@
       </c>
     </row>
     <row r="70" spans="1:20">
-      <c r="A70" s="5"/>
+      <c r="A70" s="8"/>
       <c r="B70">
         <v>14</v>
       </c>
@@ -7463,8 +5491,8 @@
       </c>
     </row>
     <row r="72" spans="1:20">
-      <c r="A72" s="5" t="s">
-        <v>20</v>
+      <c r="A72" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="B72">
         <v>-6</v>
@@ -7523,7 +5551,7 @@
       </c>
     </row>
     <row r="73" spans="1:20">
-      <c r="A73" s="5"/>
+      <c r="A73" s="8"/>
       <c r="B73">
         <v>-4</v>
       </c>
@@ -7581,7 +5609,7 @@
       </c>
     </row>
     <row r="74" spans="1:20">
-      <c r="A74" s="5"/>
+      <c r="A74" s="8"/>
       <c r="B74">
         <v>-2</v>
       </c>
@@ -7639,7 +5667,7 @@
       </c>
     </row>
     <row r="75" spans="1:20">
-      <c r="A75" s="5"/>
+      <c r="A75" s="8"/>
       <c r="B75">
         <v>0</v>
       </c>
@@ -7697,7 +5725,7 @@
       </c>
     </row>
     <row r="76" spans="1:20">
-      <c r="A76" s="5"/>
+      <c r="A76" s="8"/>
       <c r="B76">
         <v>2</v>
       </c>
@@ -7755,7 +5783,7 @@
       </c>
     </row>
     <row r="77" spans="1:20">
-      <c r="A77" s="5"/>
+      <c r="A77" s="8"/>
       <c r="B77">
         <v>4</v>
       </c>
@@ -7813,7 +5841,7 @@
       </c>
     </row>
     <row r="78" spans="1:20">
-      <c r="A78" s="5"/>
+      <c r="A78" s="8"/>
       <c r="B78">
         <v>6</v>
       </c>
@@ -7871,7 +5899,7 @@
       </c>
     </row>
     <row r="79" spans="1:20">
-      <c r="A79" s="5"/>
+      <c r="A79" s="8"/>
       <c r="B79">
         <v>8</v>
       </c>
@@ -7929,7 +5957,7 @@
       </c>
     </row>
     <row r="80" spans="1:20">
-      <c r="A80" s="5"/>
+      <c r="A80" s="8"/>
       <c r="B80">
         <v>10</v>
       </c>
@@ -7987,7 +6015,7 @@
       </c>
     </row>
     <row r="81" spans="1:20">
-      <c r="A81" s="5"/>
+      <c r="A81" s="8"/>
       <c r="B81">
         <v>11</v>
       </c>
@@ -8045,7 +6073,7 @@
       </c>
     </row>
     <row r="82" spans="1:20">
-      <c r="A82" s="5"/>
+      <c r="A82" s="8"/>
       <c r="B82">
         <v>12</v>
       </c>
@@ -8103,7 +6131,7 @@
       </c>
     </row>
     <row r="83" spans="1:20">
-      <c r="A83" s="5"/>
+      <c r="A83" s="8"/>
       <c r="B83">
         <v>13</v>
       </c>
@@ -8161,7 +6189,7 @@
       </c>
     </row>
     <row r="84" spans="1:20">
-      <c r="A84" s="5"/>
+      <c r="A84" s="8"/>
       <c r="B84">
         <v>14</v>
       </c>
@@ -8227,13 +6255,13 @@
     <mergeCell ref="A44:A56"/>
     <mergeCell ref="A58:A70"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005272B3-68E4-4311-B6FE-16E821B34AB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z84"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
@@ -8243,10 +6271,10 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C1">
         <v>0</v>
@@ -8292,8 +6320,8 @@
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="5" t="s">
-        <v>25</v>
+      <c r="A2" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="B2">
         <v>-6</v>
@@ -8349,7 +6377,7 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="5"/>
+      <c r="A3" s="8"/>
       <c r="B3">
         <v>-4</v>
       </c>
@@ -8404,7 +6432,7 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="5"/>
+      <c r="A4" s="8"/>
       <c r="B4">
         <v>-2</v>
       </c>
@@ -8459,7 +6487,7 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="5"/>
+      <c r="A5" s="8"/>
       <c r="B5">
         <v>0</v>
       </c>
@@ -8514,7 +6542,7 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="5"/>
+      <c r="A6" s="8"/>
       <c r="B6">
         <v>2</v>
       </c>
@@ -8569,7 +6597,7 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="5"/>
+      <c r="A7" s="8"/>
       <c r="B7">
         <v>4</v>
       </c>
@@ -8624,7 +6652,7 @@
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="5"/>
+      <c r="A8" s="8"/>
       <c r="B8">
         <v>6</v>
       </c>
@@ -8679,7 +6707,7 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="5"/>
+      <c r="A9" s="8"/>
       <c r="B9">
         <v>8</v>
       </c>
@@ -8734,7 +6762,7 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="5"/>
+      <c r="A10" s="8"/>
       <c r="B10">
         <v>10</v>
       </c>
@@ -8789,7 +6817,7 @@
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="5"/>
+      <c r="A11" s="8"/>
       <c r="B11">
         <v>11</v>
       </c>
@@ -8844,7 +6872,7 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="5"/>
+      <c r="A12" s="8"/>
       <c r="B12">
         <v>12</v>
       </c>
@@ -8899,7 +6927,7 @@
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="5"/>
+      <c r="A13" s="8"/>
       <c r="B13">
         <v>13</v>
       </c>
@@ -8954,7 +6982,7 @@
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="5"/>
+      <c r="A14" s="8"/>
       <c r="B14">
         <v>14</v>
       </c>
@@ -9012,8 +7040,8 @@
       <c r="A15" s="4"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="5" t="s">
-        <v>26</v>
+      <c r="A16" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B16">
         <v>-6</v>
@@ -9069,7 +7097,7 @@
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="5"/>
+      <c r="A17" s="8"/>
       <c r="B17">
         <v>-4</v>
       </c>
@@ -9124,7 +7152,7 @@
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="5"/>
+      <c r="A18" s="8"/>
       <c r="B18">
         <v>-2</v>
       </c>
@@ -9179,7 +7207,7 @@
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="5"/>
+      <c r="A19" s="8"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -9234,7 +7262,7 @@
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="5"/>
+      <c r="A20" s="8"/>
       <c r="B20">
         <v>2</v>
       </c>
@@ -9289,7 +7317,7 @@
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="5"/>
+      <c r="A21" s="8"/>
       <c r="B21">
         <v>4</v>
       </c>
@@ -9344,7 +7372,7 @@
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="5"/>
+      <c r="A22" s="8"/>
       <c r="B22">
         <v>6</v>
       </c>
@@ -9399,7 +7427,7 @@
       </c>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="5"/>
+      <c r="A23" s="8"/>
       <c r="B23">
         <v>8</v>
       </c>
@@ -9454,7 +7482,7 @@
       </c>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="5"/>
+      <c r="A24" s="8"/>
       <c r="B24">
         <v>10</v>
       </c>
@@ -9509,7 +7537,7 @@
       </c>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="5"/>
+      <c r="A25" s="8"/>
       <c r="B25">
         <v>11</v>
       </c>
@@ -9564,7 +7592,7 @@
       </c>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="5"/>
+      <c r="A26" s="8"/>
       <c r="B26">
         <v>12</v>
       </c>
@@ -9619,7 +7647,7 @@
       </c>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="5"/>
+      <c r="A27" s="8"/>
       <c r="B27">
         <v>13</v>
       </c>
@@ -9674,7 +7702,7 @@
       </c>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="5"/>
+      <c r="A28" s="8"/>
       <c r="B28">
         <v>14</v>
       </c>
@@ -9732,8 +7760,8 @@
       <c r="A29" s="4"/>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="5" t="s">
-        <v>27</v>
+      <c r="A30" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B30">
         <v>-6</v>
@@ -9789,7 +7817,7 @@
       </c>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="5"/>
+      <c r="A31" s="8"/>
       <c r="B31">
         <v>-4</v>
       </c>
@@ -9844,7 +7872,7 @@
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="5"/>
+      <c r="A32" s="8"/>
       <c r="B32">
         <v>-2</v>
       </c>
@@ -9899,7 +7927,7 @@
       </c>
     </row>
     <row r="33" spans="1:26">
-      <c r="A33" s="5"/>
+      <c r="A33" s="8"/>
       <c r="B33">
         <v>0</v>
       </c>
@@ -9954,7 +7982,7 @@
       </c>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="5"/>
+      <c r="A34" s="8"/>
       <c r="B34">
         <v>2</v>
       </c>
@@ -10009,7 +8037,7 @@
       </c>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="5"/>
+      <c r="A35" s="8"/>
       <c r="B35">
         <v>4</v>
       </c>
@@ -10064,7 +8092,7 @@
       </c>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="5"/>
+      <c r="A36" s="8"/>
       <c r="B36">
         <v>6</v>
       </c>
@@ -10119,7 +8147,7 @@
       </c>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="5"/>
+      <c r="A37" s="8"/>
       <c r="B37">
         <v>8</v>
       </c>
@@ -10174,7 +8202,7 @@
       </c>
     </row>
     <row r="38" spans="1:26">
-      <c r="A38" s="5"/>
+      <c r="A38" s="8"/>
       <c r="B38">
         <v>10</v>
       </c>
@@ -10229,7 +8257,7 @@
       </c>
     </row>
     <row r="39" spans="1:26">
-      <c r="A39" s="5"/>
+      <c r="A39" s="8"/>
       <c r="B39">
         <v>11</v>
       </c>
@@ -10284,7 +8312,7 @@
       </c>
     </row>
     <row r="40" spans="1:26">
-      <c r="A40" s="5"/>
+      <c r="A40" s="8"/>
       <c r="B40">
         <v>12</v>
       </c>
@@ -10339,7 +8367,7 @@
       </c>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="5"/>
+      <c r="A41" s="8"/>
       <c r="B41">
         <v>13</v>
       </c>
@@ -10394,7 +8422,7 @@
       </c>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="5"/>
+      <c r="A42" s="8"/>
       <c r="B42">
         <v>14</v>
       </c>
@@ -10452,8 +8480,8 @@
       <c r="A43" s="4"/>
     </row>
     <row r="44" spans="1:26">
-      <c r="A44" s="5" t="s">
-        <v>28</v>
+      <c r="A44" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="B44">
         <v>-6</v>
@@ -10537,7 +8565,7 @@
       </c>
     </row>
     <row r="45" spans="1:26">
-      <c r="A45" s="5"/>
+      <c r="A45" s="8"/>
       <c r="B45">
         <v>-4</v>
       </c>
@@ -10620,7 +8648,7 @@
       </c>
     </row>
     <row r="46" spans="1:26">
-      <c r="A46" s="5"/>
+      <c r="A46" s="8"/>
       <c r="B46">
         <v>-2</v>
       </c>
@@ -10703,7 +8731,7 @@
       </c>
     </row>
     <row r="47" spans="1:26">
-      <c r="A47" s="5"/>
+      <c r="A47" s="8"/>
       <c r="B47">
         <v>0</v>
       </c>
@@ -10786,7 +8814,7 @@
       </c>
     </row>
     <row r="48" spans="1:26">
-      <c r="A48" s="5"/>
+      <c r="A48" s="8"/>
       <c r="B48">
         <v>2</v>
       </c>
@@ -10869,7 +8897,7 @@
       </c>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="5"/>
+      <c r="A49" s="8"/>
       <c r="B49">
         <v>4</v>
       </c>
@@ -10952,7 +8980,7 @@
       </c>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="5"/>
+      <c r="A50" s="8"/>
       <c r="B50">
         <v>6</v>
       </c>
@@ -11035,7 +9063,7 @@
       </c>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="5"/>
+      <c r="A51" s="8"/>
       <c r="B51">
         <v>8</v>
       </c>
@@ -11118,7 +9146,7 @@
       </c>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="5"/>
+      <c r="A52" s="8"/>
       <c r="B52">
         <v>10</v>
       </c>
@@ -11201,7 +9229,7 @@
       </c>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="5"/>
+      <c r="A53" s="8"/>
       <c r="B53">
         <v>11</v>
       </c>
@@ -11284,7 +9312,7 @@
       </c>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="5"/>
+      <c r="A54" s="8"/>
       <c r="B54">
         <v>12</v>
       </c>
@@ -11367,7 +9395,7 @@
       </c>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="5"/>
+      <c r="A55" s="8"/>
       <c r="B55">
         <v>13</v>
       </c>
@@ -11450,7 +9478,7 @@
       </c>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="5"/>
+      <c r="A56" s="8"/>
       <c r="B56">
         <v>14</v>
       </c>
@@ -11536,8 +9564,8 @@
       <c r="A57" s="4"/>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="5" t="s">
-        <v>29</v>
+      <c r="A58" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="B58">
         <v>-6</v>
@@ -11621,7 +9649,7 @@
       </c>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="5"/>
+      <c r="A59" s="8"/>
       <c r="B59">
         <v>-4</v>
       </c>
@@ -11704,7 +9732,7 @@
       </c>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="5"/>
+      <c r="A60" s="8"/>
       <c r="B60">
         <v>-2</v>
       </c>
@@ -11787,7 +9815,7 @@
       </c>
     </row>
     <row r="61" spans="1:26">
-      <c r="A61" s="5"/>
+      <c r="A61" s="8"/>
       <c r="B61">
         <v>0</v>
       </c>
@@ -11870,7 +9898,7 @@
       </c>
     </row>
     <row r="62" spans="1:26">
-      <c r="A62" s="5"/>
+      <c r="A62" s="8"/>
       <c r="B62">
         <v>2</v>
       </c>
@@ -11953,7 +9981,7 @@
       </c>
     </row>
     <row r="63" spans="1:26">
-      <c r="A63" s="5"/>
+      <c r="A63" s="8"/>
       <c r="B63">
         <v>4</v>
       </c>
@@ -12036,7 +10064,7 @@
       </c>
     </row>
     <row r="64" spans="1:26">
-      <c r="A64" s="5"/>
+      <c r="A64" s="8"/>
       <c r="B64">
         <v>6</v>
       </c>
@@ -12119,7 +10147,7 @@
       </c>
     </row>
     <row r="65" spans="1:26">
-      <c r="A65" s="5"/>
+      <c r="A65" s="8"/>
       <c r="B65">
         <v>8</v>
       </c>
@@ -12202,7 +10230,7 @@
       </c>
     </row>
     <row r="66" spans="1:26">
-      <c r="A66" s="5"/>
+      <c r="A66" s="8"/>
       <c r="B66">
         <v>10</v>
       </c>
@@ -12285,7 +10313,7 @@
       </c>
     </row>
     <row r="67" spans="1:26">
-      <c r="A67" s="5"/>
+      <c r="A67" s="8"/>
       <c r="B67">
         <v>11</v>
       </c>
@@ -12368,7 +10396,7 @@
       </c>
     </row>
     <row r="68" spans="1:26">
-      <c r="A68" s="5"/>
+      <c r="A68" s="8"/>
       <c r="B68">
         <v>12</v>
       </c>
@@ -12451,7 +10479,7 @@
       </c>
     </row>
     <row r="69" spans="1:26">
-      <c r="A69" s="5"/>
+      <c r="A69" s="8"/>
       <c r="B69">
         <v>13</v>
       </c>
@@ -12534,7 +10562,7 @@
       </c>
     </row>
     <row r="70" spans="1:26">
-      <c r="A70" s="5"/>
+      <c r="A70" s="8"/>
       <c r="B70">
         <v>14</v>
       </c>
@@ -12620,8 +10648,8 @@
       <c r="A71" s="4"/>
     </row>
     <row r="72" spans="1:26">
-      <c r="A72" s="5" t="s">
-        <v>30</v>
+      <c r="A72" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="B72">
         <v>-6</v>
@@ -12705,7 +10733,7 @@
       </c>
     </row>
     <row r="73" spans="1:26">
-      <c r="A73" s="5"/>
+      <c r="A73" s="8"/>
       <c r="B73">
         <v>-4</v>
       </c>
@@ -12788,7 +10816,7 @@
       </c>
     </row>
     <row r="74" spans="1:26">
-      <c r="A74" s="5"/>
+      <c r="A74" s="8"/>
       <c r="B74">
         <v>-2</v>
       </c>
@@ -12871,7 +10899,7 @@
       </c>
     </row>
     <row r="75" spans="1:26">
-      <c r="A75" s="5"/>
+      <c r="A75" s="8"/>
       <c r="B75">
         <v>0</v>
       </c>
@@ -12954,7 +10982,7 @@
       </c>
     </row>
     <row r="76" spans="1:26">
-      <c r="A76" s="5"/>
+      <c r="A76" s="8"/>
       <c r="B76">
         <v>2</v>
       </c>
@@ -13037,7 +11065,7 @@
       </c>
     </row>
     <row r="77" spans="1:26">
-      <c r="A77" s="5"/>
+      <c r="A77" s="8"/>
       <c r="B77">
         <v>4</v>
       </c>
@@ -13120,7 +11148,7 @@
       </c>
     </row>
     <row r="78" spans="1:26">
-      <c r="A78" s="5"/>
+      <c r="A78" s="8"/>
       <c r="B78">
         <v>6</v>
       </c>
@@ -13203,7 +11231,7 @@
       </c>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="5"/>
+      <c r="A79" s="8"/>
       <c r="B79">
         <v>8</v>
       </c>
@@ -13286,7 +11314,7 @@
       </c>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="5"/>
+      <c r="A80" s="8"/>
       <c r="B80">
         <v>10</v>
       </c>
@@ -13369,7 +11397,7 @@
       </c>
     </row>
     <row r="81" spans="1:26">
-      <c r="A81" s="5"/>
+      <c r="A81" s="8"/>
       <c r="B81">
         <v>11</v>
       </c>
@@ -13452,7 +11480,7 @@
       </c>
     </row>
     <row r="82" spans="1:26">
-      <c r="A82" s="5"/>
+      <c r="A82" s="8"/>
       <c r="B82">
         <v>12</v>
       </c>
@@ -13535,7 +11563,7 @@
       </c>
     </row>
     <row r="83" spans="1:26">
-      <c r="A83" s="5"/>
+      <c r="A83" s="8"/>
       <c r="B83">
         <v>13</v>
       </c>
@@ -13618,7 +11646,7 @@
       </c>
     </row>
     <row r="84" spans="1:26">
-      <c r="A84" s="5"/>
+      <c r="A84" s="8"/>
       <c r="B84">
         <v>14</v>
       </c>
@@ -13709,18 +11737,18 @@
     <mergeCell ref="A44:A56"/>
     <mergeCell ref="A58:A70"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6172478-EC75-43C1-9FB0-A15B71A2EF1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" customWidth="1"/>
     <col min="6" max="6" width="12.109375" customWidth="1"/>
@@ -13730,28 +11758,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -13917,28 +11945,28 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -14104,28 +12132,28 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -14327,28 +12355,28 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G28" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -14532,25 +12560,25 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F37" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G37" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -14624,25 +12652,25 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G42" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -14807,17 +12835,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="C21:C22 D22 C24:C25 E21:E22 D24:D25 F24:F25" formula="1"/>
-  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB2D269-1CEB-4E31-875B-88666882F966}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
@@ -14831,7 +12856,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>-45.848999999999997</v>
@@ -14839,7 +12864,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>-3.0775999999999999</v>
@@ -14847,7 +12872,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>13.004</v>
@@ -14855,7 +12880,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>5.8177000000000003</v>
@@ -14863,7 +12888,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>-0.62892999999999999</v>
@@ -14871,7 +12896,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0.15584999999999999</v>
@@ -14879,7 +12904,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>-0.11662</v>
@@ -14887,7 +12912,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>2.0151000000000001E-3</v>
@@ -14895,7 +12920,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>-0.36527999999999999</v>
@@ -14903,7 +12928,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0.36157</v>
@@ -14911,7 +12936,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>2.4550000000000001</v>
@@ -14919,7 +12944,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0.42899999999999999</v>
@@ -14927,14 +12952,125 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="6"/>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="6"/>
+      <c r="B16" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>